--- a/data/trans_orig/P6701-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6701-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen que trabajar muy rápido en 2012</t>
+          <t>Población según si tienen que trabajar muy rápido en 2012 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9532</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25983</t>
+          <t>24610</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21306</t>
+          <t>20901</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43419</t>
+          <t>40842</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34129</t>
+          <t>33758</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59863</t>
+          <t>60709</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11824</t>
+          <t>11332</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28885</t>
+          <t>29290</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,82 +860,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>15,92%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>18878</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11592</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>27572</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>13,49%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>8,28%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>19,7%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>37619</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>27372</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>50868</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>11,61%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>15,7%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18878</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>11500</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>27532</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>13,49%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>8,22%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>19,67%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>37619</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>26989</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>50280</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>11,61%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68981</t>
+          <t>68589</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95863</t>
+          <t>95294</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33685</t>
+          <t>34220</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56220</t>
+          <t>56544</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>108942</t>
+          <t>108593</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>143664</t>
+          <t>144255</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,52%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27964</t>
+          <t>29813</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51372</t>
+          <t>52202</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11953</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30598</t>
+          <t>28001</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44610</t>
+          <t>44867</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72838</t>
+          <t>73707</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19721</t>
+          <t>20159</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39623</t>
+          <t>38963</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18258</t>
+          <t>18300</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37638</t>
+          <t>36855</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43169</t>
+          <t>43022</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69838</t>
+          <t>71664</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59983</t>
+          <t>62018</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>95397</t>
+          <t>97009</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41888</t>
+          <t>42068</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71367</t>
+          <t>71609</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>110836</t>
+          <t>109556</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>155170</t>
+          <t>156445</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76028</t>
+          <t>75116</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>114314</t>
+          <t>114258</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41423</t>
+          <t>42135</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70141</t>
+          <t>70803</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>126370</t>
+          <t>125794</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>175923</t>
+          <t>177663</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>298785</t>
+          <t>298872</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>362134</t>
+          <t>358847</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166697</t>
+          <t>165840</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>209535</t>
+          <t>210671</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>480295</t>
+          <t>477682</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>554412</t>
+          <t>555196</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,28%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>201455</t>
+          <t>200174</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>254224</t>
+          <t>252517</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>127427</t>
+          <t>127200</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>171532</t>
+          <t>171766</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>342774</t>
+          <t>342146</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>414604</t>
+          <t>408294</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>168542</t>
+          <t>166196</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>217357</t>
+          <t>216891</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>106471</t>
+          <t>107410</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>146084</t>
+          <t>145997</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>287040</t>
+          <t>280240</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>351357</t>
+          <t>348661</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22454</t>
+          <t>24443</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45887</t>
+          <t>47695</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19401</t>
+          <t>18605</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41755</t>
+          <t>41677</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49326</t>
+          <t>48725</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>79101</t>
+          <t>81322</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28638</t>
+          <t>29552</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53759</t>
+          <t>54650</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23058</t>
+          <t>23143</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45901</t>
+          <t>46473</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>57679</t>
+          <t>57994</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>92120</t>
+          <t>92617</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>103476</t>
+          <t>103248</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>141500</t>
+          <t>141375</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>78650</t>
+          <t>78173</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>111669</t>
+          <t>109753</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>195197</t>
+          <t>192658</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>244768</t>
+          <t>241906</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>43,89%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57661</t>
+          <t>58625</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>91850</t>
+          <t>89460</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26253</t>
+          <t>26289</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51754</t>
+          <t>51425</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>91241</t>
+          <t>89013</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>130300</t>
+          <t>129744</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34618</t>
+          <t>33253</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60964</t>
+          <t>60673</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31463</t>
+          <t>31486</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55817</t>
+          <t>55282</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>70060</t>
+          <t>71573</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>105391</t>
+          <t>108273</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>105118</t>
+          <t>104061</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>151875</t>
+          <t>148147</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>96109</t>
+          <t>93780</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>137476</t>
+          <t>135778</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>211715</t>
+          <t>210726</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>273792</t>
+          <t>273763</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>129313</t>
+          <t>127095</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>180551</t>
+          <t>177652</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>86189</t>
+          <t>88831</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>127659</t>
+          <t>128280</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>228301</t>
+          <t>228366</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>290685</t>
+          <t>290459</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>499468</t>
+          <t>496615</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>575945</t>
+          <t>569449</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>294076</t>
+          <t>296135</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>355424</t>
+          <t>356011</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>811279</t>
+          <t>811727</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>913562</t>
+          <t>907306</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,37%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>305252</t>
+          <t>306877</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>376269</t>
+          <t>371883</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>180951</t>
+          <t>179467</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>232445</t>
+          <t>235003</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>503250</t>
+          <t>503148</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>584968</t>
+          <t>587141</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>236363</t>
+          <t>234928</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>297293</t>
+          <t>295726</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>169330</t>
+          <t>169102</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>220296</t>
+          <t>220069</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>422691</t>
+          <t>423722</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>503241</t>
+          <t>503792</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen que trabajar muy rápido en 2016</t>
+          <t>Población según si tienen que trabajar muy rápido en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15582</t>
+          <t>15231</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17224</t>
+          <t>17233</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11507</t>
+          <t>10951</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29531</t>
+          <t>27921</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18142</t>
+          <t>17643</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14195</t>
+          <t>14044</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11029</t>
+          <t>10780</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26332</t>
+          <t>27856</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44653</t>
+          <t>44448</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68133</t>
+          <t>68146</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18690</t>
+          <t>18687</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35556</t>
+          <t>33828</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>68804</t>
+          <t>67731</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>96577</t>
+          <t>97165</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>45,15%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29322</t>
+          <t>29472</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50153</t>
+          <t>50474</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18921</t>
+          <t>18912</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39374</t>
+          <t>39905</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64831</t>
+          <t>64346</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,9%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20124</t>
+          <t>20523</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40132</t>
+          <t>41620</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9396</t>
+          <t>10427</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23541</t>
+          <t>24530</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34924</t>
+          <t>33848</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>59505</t>
+          <t>58256</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46553</t>
+          <t>45376</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77818</t>
+          <t>78043</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36421</t>
+          <t>36394</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62975</t>
+          <t>64086</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89748</t>
+          <t>88008</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>127363</t>
+          <t>128561</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79075</t>
+          <t>79913</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>119277</t>
+          <t>119430</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61537</t>
+          <t>60486</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93343</t>
+          <t>93777</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>151050</t>
+          <t>150865</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>200714</t>
+          <t>199464</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>275782</t>
+          <t>275881</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>336751</t>
+          <t>332831</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>227831</t>
+          <t>228367</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>278554</t>
+          <t>277003</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>519019</t>
+          <t>520128</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>595917</t>
+          <t>594342</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,66%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>259518</t>
+          <t>258037</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>316214</t>
+          <t>317825</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>143833</t>
+          <t>141159</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>187209</t>
+          <t>187428</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>414129</t>
+          <t>412724</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>487799</t>
+          <t>483055</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>152103</t>
+          <t>153281</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>200661</t>
+          <t>203155</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,82 +4840,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>16,57%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>21,96%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>113270</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>94389</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>134433</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>17,35%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>14,46%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>20,59%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>289276</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>259468</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>319732</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>18,33%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>16,44%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>21,69%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>113270</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>93468</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>133391</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>17,35%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>14,32%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>20,43%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>289276</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>257456</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>321626</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>18,33%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>16,32%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18936</t>
+          <t>19230</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39732</t>
+          <t>38570</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18551</t>
+          <t>19120</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39252</t>
+          <t>40579</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42924</t>
+          <t>42162</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>73184</t>
+          <t>72690</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47346</t>
+          <t>46112</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76830</t>
+          <t>75373</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38810</t>
+          <t>36890</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64108</t>
+          <t>64176</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>92649</t>
+          <t>92124</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>132486</t>
+          <t>131782</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>124212</t>
+          <t>125136</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>162548</t>
+          <t>163486</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>98514</t>
+          <t>98224</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>129159</t>
+          <t>131296</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>232401</t>
+          <t>232955</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>284125</t>
+          <t>285322</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,29%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53802</t>
+          <t>53318</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>84367</t>
+          <t>83862</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49036</t>
+          <t>48420</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>76053</t>
+          <t>75646</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>109378</t>
+          <t>109284</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>151298</t>
+          <t>152280</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37342</t>
+          <t>38438</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>65931</t>
+          <t>66189</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43107</t>
+          <t>42199</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>69873</t>
+          <t>70476</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>85583</t>
+          <t>87741</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>127060</t>
+          <t>125122</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,98%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>77863</t>
+          <t>78380</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>117012</t>
+          <t>116043</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>68654</t>
+          <t>70658</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>103668</t>
+          <t>104949</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>157941</t>
+          <t>156738</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>212023</t>
+          <t>212871</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>146133</t>
+          <t>145207</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>196422</t>
+          <t>195508</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>113450</t>
+          <t>110929</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>156689</t>
+          <t>155377</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>271626</t>
+          <t>273738</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>338300</t>
+          <t>336664</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>468687</t>
+          <t>470600</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>540341</t>
+          <t>545323</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>362430</t>
+          <t>360499</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424769</t>
+          <t>422737</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>848489</t>
+          <t>842002</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>943252</t>
+          <t>945252</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,55%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>362002</t>
+          <t>360941</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>432629</t>
+          <t>426485</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>212488</t>
+          <t>208869</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>263269</t>
+          <t>262795</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>587854</t>
+          <t>584623</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>680068</t>
+          <t>673071</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,45%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>228312</t>
+          <t>226781</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>286730</t>
+          <t>286543</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>160665</t>
+          <t>161613</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>212622</t>
+          <t>210483</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>400479</t>
+          <t>402965</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>478262</t>
+          <t>482099</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen que trabajar muy rápido en 2023</t>
+          <t>Población según si tienen que trabajar muy rápido en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>8968</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>175</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2318</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11730</t>
+          <t>11285</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4454</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>910</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12766</t>
+          <t>12469</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24734</t>
+          <t>24584</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>9261</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17135</t>
+          <t>17492</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31479</t>
+          <t>32154</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>62,87%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2531</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11016</t>
+          <t>11268</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7929</t>
+          <t>8029</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>6193</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16604</t>
+          <t>17033</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>33,3%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>331</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8695</t>
+          <t>9398</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12735</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43628</t>
+          <t>44422</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>429526</t>
+          <t>442384</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,82 +7347,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>8,68%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>86,44%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>20542</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>14378</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>28056</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>8,89%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>12,14%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>292103</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>63293</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>545439</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>39,32%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>8,52%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>83,92%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>20542</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>14399</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>28817</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,89%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>6,23%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>12,47%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>292103</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>64726</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>563646</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>39,32%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>8,71%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>73,42%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9316</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70754</t>
+          <t>70824</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14884</t>
+          <t>15276</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30924</t>
+          <t>31081</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17707</t>
+          <t>22845</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>87773</t>
+          <t>90167</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27985</t>
+          <t>24508</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>191641</t>
+          <t>187756</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>60110</t>
+          <t>59534</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>83842</t>
+          <t>83094</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>67143</t>
+          <t>69807</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>253682</t>
+          <t>260085</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>35,01%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24972</t>
+          <t>20803</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>153008</t>
+          <t>157962</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59021</t>
+          <t>57418</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83981</t>
+          <t>81637</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59089</t>
+          <t>63956</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>228250</t>
+          <t>226956</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9263</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>83383</t>
+          <t>83061</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38200</t>
+          <t>36771</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60052</t>
+          <t>60571</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32472</t>
+          <t>34972</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>140416</t>
+          <t>138696</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31425</t>
+          <t>31392</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55924</t>
+          <t>54893</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21614</t>
+          <t>21846</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38969</t>
+          <t>39639</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58945</t>
+          <t>59473</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87780</t>
+          <t>88227</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,21%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23333</t>
+          <t>24112</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12496</t>
+          <t>12176</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26894</t>
+          <t>26816</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21610</t>
+          <t>22404</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43883</t>
+          <t>43680</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27134</t>
+          <t>27512</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50823</t>
+          <t>51245</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28596</t>
+          <t>28859</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46351</t>
+          <t>46586</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>61629</t>
+          <t>61947</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>89311</t>
+          <t>89709</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>12758</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33346</t>
+          <t>32118</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19110</t>
+          <t>18235</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23095</t>
+          <t>23665</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45664</t>
+          <t>45900</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5642</t>
+          <t>5481</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18637</t>
+          <t>18866</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15557</t>
+          <t>16218</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12402</t>
+          <t>12136</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>28716</t>
+          <t>29066</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>107894</t>
+          <t>110710</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>535061</t>
+          <t>527350</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40521</t>
+          <t>40616</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>65277</t>
+          <t>65763</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>156484</t>
+          <t>159379</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>683923</t>
+          <t>718248</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>70,08%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17239</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>80823</t>
+          <t>80546</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>33666</t>
+          <t>31853</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>54987</t>
+          <t>54210</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>39340</t>
+          <t>40983</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>127560</t>
+          <t>125985</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>56207</t>
+          <t>55799</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>245966</t>
+          <t>249802</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>97147</t>
+          <t>98007</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>128210</t>
+          <t>128145</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>133102</t>
+          <t>121253</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>357846</t>
+          <t>357903</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,92%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34780</t>
+          <t>40799</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>171615</t>
+          <t>169223</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>73245</t>
+          <t>72169</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>103174</t>
+          <t>100388</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>95401</t>
+          <t>84246</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>257682</t>
+          <t>253221</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18216</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>89647</t>
+          <t>89015</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48522</t>
+          <t>47664</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>74269</t>
+          <t>73791</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>51063</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>155680</t>
+          <t>154954</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6701-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6701-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24610</t>
+          <t>24547</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20901</t>
+          <t>21272</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40842</t>
+          <t>41847</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33758</t>
+          <t>34521</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60709</t>
+          <t>59658</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11332</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29290</t>
+          <t>28825</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11592</t>
+          <t>11654</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27572</t>
+          <t>27489</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27372</t>
+          <t>26746</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50868</t>
+          <t>50804</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68589</t>
+          <t>69621</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95294</t>
+          <t>96228</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34220</t>
+          <t>34658</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56544</t>
+          <t>57409</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>108593</t>
+          <t>109203</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>144255</t>
+          <t>144299</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,54%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29813</t>
+          <t>27634</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52202</t>
+          <t>50524</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>12039</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28001</t>
+          <t>28911</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44867</t>
+          <t>44205</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73707</t>
+          <t>74289</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20159</t>
+          <t>20522</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38963</t>
+          <t>39323</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18300</t>
+          <t>18482</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36855</t>
+          <t>37574</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43022</t>
+          <t>43039</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71664</t>
+          <t>70243</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62018</t>
+          <t>57426</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>97009</t>
+          <t>94588</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42068</t>
+          <t>42371</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71609</t>
+          <t>71934</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>109556</t>
+          <t>112099</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>156445</t>
+          <t>155928</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75116</t>
+          <t>74591</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>114258</t>
+          <t>114123</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42135</t>
+          <t>40943</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70803</t>
+          <t>69814</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>125794</t>
+          <t>126405</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>177663</t>
+          <t>175765</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>298872</t>
+          <t>298790</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>358847</t>
+          <t>360521</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>165840</t>
+          <t>164992</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>210671</t>
+          <t>211621</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>477682</t>
+          <t>478913</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>555196</t>
+          <t>553909</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,19%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>200174</t>
+          <t>200921</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>252517</t>
+          <t>252717</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>127200</t>
+          <t>127642</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>171766</t>
+          <t>170156</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>342146</t>
+          <t>343388</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>408294</t>
+          <t>408993</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,46%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>166196</t>
+          <t>166466</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>216891</t>
+          <t>216748</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>107410</t>
+          <t>106148</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>145997</t>
+          <t>146305</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>280240</t>
+          <t>283423</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>348661</t>
+          <t>348589</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24443</t>
+          <t>24875</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47695</t>
+          <t>47945</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18605</t>
+          <t>19446</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41677</t>
+          <t>41528</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>48725</t>
+          <t>47097</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81322</t>
+          <t>79653</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29552</t>
+          <t>29211</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54650</t>
+          <t>54232</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23143</t>
+          <t>23643</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46473</t>
+          <t>46463</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>57994</t>
+          <t>58767</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>92617</t>
+          <t>92745</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>103248</t>
+          <t>106766</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>141375</t>
+          <t>142546</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>78173</t>
+          <t>77044</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>109753</t>
+          <t>109670</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>192658</t>
+          <t>191709</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>241906</t>
+          <t>242671</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>58625</t>
+          <t>57754</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>89460</t>
+          <t>90358</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26289</t>
+          <t>26125</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51425</t>
+          <t>50288</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>89013</t>
+          <t>91726</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>129744</t>
+          <t>131943</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,94%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33253</t>
+          <t>32785</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60673</t>
+          <t>59502</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31486</t>
+          <t>31047</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55282</t>
+          <t>55795</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>71573</t>
+          <t>71524</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>108273</t>
+          <t>109465</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>104061</t>
+          <t>104148</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>148147</t>
+          <t>149578</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>93780</t>
+          <t>95003</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>135778</t>
+          <t>137116</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>210726</t>
+          <t>210919</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>273763</t>
+          <t>274245</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>127095</t>
+          <t>127755</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>177652</t>
+          <t>176894</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>88831</t>
+          <t>89334</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>128280</t>
+          <t>128339</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>228366</t>
+          <t>228968</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>290459</t>
+          <t>292638</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>496615</t>
+          <t>499276</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>569449</t>
+          <t>576079</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>296135</t>
+          <t>294905</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>356011</t>
+          <t>355629</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>811727</t>
+          <t>809599</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>907306</t>
+          <t>905643</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,3%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>306877</t>
+          <t>302670</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>371883</t>
+          <t>370987</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>179467</t>
+          <t>181137</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>235003</t>
+          <t>234093</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>503148</t>
+          <t>505098</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>587141</t>
+          <t>585691</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>234928</t>
+          <t>237033</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>295726</t>
+          <t>296326</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>169102</t>
+          <t>166737</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>220069</t>
+          <t>218780</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>423722</t>
+          <t>419761</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>503792</t>
+          <t>496379</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3984</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15231</t>
+          <t>15039</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17233</t>
+          <t>16803</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10951</t>
+          <t>10972</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27921</t>
+          <t>27347</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>5257</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17643</t>
+          <t>17654</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3791</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14044</t>
+          <t>14134</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10780</t>
+          <t>10751</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27856</t>
+          <t>27676</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>44608</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68146</t>
+          <t>68590</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18687</t>
+          <t>19028</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33828</t>
+          <t>34815</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>67731</t>
+          <t>67435</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>97165</t>
+          <t>96066</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>44,64%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29472</t>
+          <t>29488</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50474</t>
+          <t>52053</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6868</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18912</t>
+          <t>19532</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39905</t>
+          <t>39558</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64346</t>
+          <t>65287</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20523</t>
+          <t>21069</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41620</t>
+          <t>41267</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10427</t>
+          <t>10417</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>24748</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33848</t>
+          <t>34116</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>58256</t>
+          <t>58573</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45376</t>
+          <t>46808</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78043</t>
+          <t>79724</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36394</t>
+          <t>36206</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64086</t>
+          <t>60577</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88008</t>
+          <t>87492</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>128561</t>
+          <t>129434</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79913</t>
+          <t>79462</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>119430</t>
+          <t>120138</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60486</t>
+          <t>60535</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93777</t>
+          <t>91659</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>150865</t>
+          <t>148069</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>199464</t>
+          <t>199672</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>275881</t>
+          <t>276618</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>332831</t>
+          <t>335374</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>228367</t>
+          <t>228608</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>277003</t>
+          <t>276379</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>520128</t>
+          <t>515586</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>594342</t>
+          <t>594898</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,7%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>258037</t>
+          <t>256944</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>317825</t>
+          <t>315184</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>141159</t>
+          <t>140249</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>187428</t>
+          <t>185740</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>412724</t>
+          <t>411427</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>483055</t>
+          <t>485037</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,74%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>153281</t>
+          <t>152125</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>203155</t>
+          <t>201594</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>94389</t>
+          <t>94978</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134433</t>
+          <t>133417</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>259468</t>
+          <t>258814</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>319732</t>
+          <t>323565</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19230</t>
+          <t>18289</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38570</t>
+          <t>39034</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19120</t>
+          <t>19329</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40579</t>
+          <t>39952</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42162</t>
+          <t>43504</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72690</t>
+          <t>72645</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46112</t>
+          <t>46232</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>75373</t>
+          <t>76092</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36890</t>
+          <t>38284</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64176</t>
+          <t>66003</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>92124</t>
+          <t>93356</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>131782</t>
+          <t>132222</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>125136</t>
+          <t>122627</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>163486</t>
+          <t>161896</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>98224</t>
+          <t>97971</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>131296</t>
+          <t>130042</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>232955</t>
+          <t>231408</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>285322</t>
+          <t>281291</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>42,68%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53318</t>
+          <t>53157</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>83862</t>
+          <t>85750</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48420</t>
+          <t>46454</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>75646</t>
+          <t>74675</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>109284</t>
+          <t>111433</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>152280</t>
+          <t>154097</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38438</t>
+          <t>38274</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66189</t>
+          <t>65335</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42199</t>
+          <t>42238</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>70476</t>
+          <t>70941</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>87741</t>
+          <t>87075</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>125122</t>
+          <t>126001</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>78380</t>
+          <t>78626</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>116043</t>
+          <t>118519</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>70658</t>
+          <t>70081</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>104949</t>
+          <t>105629</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>156738</t>
+          <t>158465</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>212871</t>
+          <t>211396</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>145207</t>
+          <t>144762</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>195508</t>
+          <t>195964</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>110929</t>
+          <t>113382</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>155377</t>
+          <t>155947</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>273738</t>
+          <t>272628</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>336664</t>
+          <t>340650</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>470600</t>
+          <t>472894</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>545323</t>
+          <t>542445</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>360499</t>
+          <t>361887</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>422737</t>
+          <t>423850</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>842002</t>
+          <t>847585</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>945252</t>
+          <t>940361</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>360941</t>
+          <t>358889</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>426485</t>
+          <t>427760</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>208869</t>
+          <t>209174</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>262795</t>
+          <t>263661</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>584623</t>
+          <t>586825</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>673071</t>
+          <t>673879</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>226781</t>
+          <t>223405</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>286543</t>
+          <t>286570</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>161613</t>
+          <t>160672</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>210483</t>
+          <t>210374</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>402965</t>
+          <t>401603</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>482099</t>
+          <t>479307</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -6645,32 +6645,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8968</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6680,32 +6680,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>505</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4207</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6715,32 +6715,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5544</t>
+          <t>6049</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11285</t>
+          <t>12214</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>825</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -6768,12 +6768,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6793,32 +6793,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>9419</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6828,32 +6828,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>11249</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -6871,32 +6871,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18847</t>
+          <t>19886</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12469</t>
+          <t>12142</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24584</t>
+          <t>27849</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6906,32 +6906,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5939</t>
+          <t>7962</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9261</t>
+          <t>12889</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6941,32 +6941,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>24786</t>
+          <t>27848</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17492</t>
+          <t>18751</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32154</t>
+          <t>37579</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>57,77%</t>
         </is>
       </c>
     </row>
@@ -6984,32 +6984,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6123</t>
+          <t>7286</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11268</t>
+          <t>14714</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7019,32 +7019,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2212</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8029</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7054,32 +7054,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>10649</t>
+          <t>12283</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6193</t>
+          <t>6773</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17033</t>
+          <t>18683</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -7097,32 +7097,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>9242</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>20029</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7132,32 +7132,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7167,32 +7167,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>13412</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13127</t>
+          <t>25999</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>39,97%</t>
         </is>
       </c>
     </row>
@@ -7210,17 +7210,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7245,17 +7245,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7280,17 +7280,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>65048</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>65048</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>65048</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7327,32 +7327,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>271561</t>
+          <t>30629</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44422</t>
+          <t>21211</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>442384</t>
+          <t>43032</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7362,32 +7362,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20542</t>
+          <t>25354</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14378</t>
+          <t>18853</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28056</t>
+          <t>34732</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7397,32 +7397,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>292103</t>
+          <t>55983</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63293</t>
+          <t>42459</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>545439</t>
+          <t>70078</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -7440,32 +7440,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33026</t>
+          <t>34143</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7546</t>
+          <t>23306</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70824</t>
+          <t>48518</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7475,32 +7475,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22047</t>
+          <t>23441</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15276</t>
+          <t>16622</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31081</t>
+          <t>32638</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7510,32 +7510,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>55073</t>
+          <t>57584</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>44607</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>90167</t>
+          <t>74114</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -7553,32 +7553,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>93760</t>
+          <t>104338</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24508</t>
+          <t>86785</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>187756</t>
+          <t>123629</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7588,32 +7588,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>70833</t>
+          <t>76441</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59534</t>
+          <t>64409</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>83094</t>
+          <t>89083</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7623,32 +7623,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>164593</t>
+          <t>180779</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>69807</t>
+          <t>160219</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>260085</t>
+          <t>202579</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>36,57%</t>
         </is>
       </c>
     </row>
@@ -7666,32 +7666,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>75643</t>
+          <t>85409</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>68403</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>157962</t>
+          <t>103627</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7701,32 +7701,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>69581</t>
+          <t>77189</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57418</t>
+          <t>63901</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81637</t>
+          <t>90521</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7736,32 +7736,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>145224</t>
+          <t>162597</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63956</t>
+          <t>141277</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>226956</t>
+          <t>184746</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>33,35%</t>
         </is>
       </c>
     </row>
@@ -7779,32 +7779,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>37814</t>
+          <t>42885</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9184</t>
+          <t>28413</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>83061</t>
+          <t>60995</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7814,32 +7814,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>48099</t>
+          <t>54179</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36771</t>
+          <t>42587</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60571</t>
+          <t>66068</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7849,32 +7849,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>85913</t>
+          <t>97063</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34972</t>
+          <t>78391</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>138696</t>
+          <t>119086</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -7892,17 +7892,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>511804</t>
+          <t>297403</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>511804</t>
+          <t>297403</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>511804</t>
+          <t>297403</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7927,17 +7927,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>231102</t>
+          <t>256603</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>231102</t>
+          <t>256603</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>231102</t>
+          <t>256603</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7962,17 +7962,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>742906</t>
+          <t>554006</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>742906</t>
+          <t>554006</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>742906</t>
+          <t>554006</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8009,27 +8009,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>42736</t>
+          <t>47941</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31392</t>
+          <t>35647</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54893</t>
+          <t>61353</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -8044,32 +8044,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>30247</t>
+          <t>31752</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21846</t>
+          <t>23532</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39639</t>
+          <t>40789</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8079,32 +8079,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>72983</t>
+          <t>79693</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59473</t>
+          <t>64673</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>88227</t>
+          <t>94818</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -8122,32 +8122,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13281</t>
+          <t>15029</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24112</t>
+          <t>26443</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8157,32 +8157,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>18735</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12176</t>
+          <t>12666</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26816</t>
+          <t>26294</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8192,32 +8192,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>31463</t>
+          <t>33764</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22404</t>
+          <t>23295</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43680</t>
+          <t>46825</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -8235,32 +8235,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>38170</t>
+          <t>41491</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27512</t>
+          <t>29475</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51245</t>
+          <t>55366</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8270,32 +8270,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>36698</t>
+          <t>39378</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28859</t>
+          <t>30923</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46586</t>
+          <t>48052</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8305,32 +8305,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74868</t>
+          <t>80869</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>61947</t>
+          <t>66987</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>89709</t>
+          <t>97653</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,27%</t>
         </is>
       </c>
     </row>
@@ -8348,32 +8348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20434</t>
+          <t>23958</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12758</t>
+          <t>14824</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32118</t>
+          <t>39384</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8383,32 +8383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12106</t>
+          <t>16139</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>10720</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18235</t>
+          <t>24384</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8418,32 +8418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>32539</t>
+          <t>40096</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23665</t>
+          <t>28331</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45900</t>
+          <t>54926</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -8461,32 +8461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>11522</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5481</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18866</t>
+          <t>20427</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8496,32 +8496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8469</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16218</t>
+          <t>15354</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8531,32 +8531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>19063</t>
+          <t>20724</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12136</t>
+          <t>13045</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>29066</t>
+          <t>32517</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -8574,17 +8574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>125215</t>
+          <t>139941</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>125215</t>
+          <t>139941</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>125215</t>
+          <t>139941</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8609,17 +8609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>105701</t>
+          <t>115206</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>105701</t>
+          <t>115206</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>105701</t>
+          <t>115206</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8644,17 +8644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>230916</t>
+          <t>255147</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>230916</t>
+          <t>255147</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>230916</t>
+          <t>255147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8691,32 +8691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>318468</t>
+          <t>82760</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>110710</t>
+          <t>64369</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>527350</t>
+          <t>102536</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8726,32 +8726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>52162</t>
+          <t>58965</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40616</t>
+          <t>47129</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>65763</t>
+          <t>72275</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8761,32 +8761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>370630</t>
+          <t>141725</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>159379</t>
+          <t>118344</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>718248</t>
+          <t>165849</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -8804,32 +8804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>47114</t>
+          <t>49997</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>36512</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>80546</t>
+          <t>66806</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8839,32 +8839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>42588</t>
+          <t>46807</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31853</t>
+          <t>36463</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>54210</t>
+          <t>59893</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8874,32 +8874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>89702</t>
+          <t>96804</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>40983</t>
+          <t>79051</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>125985</t>
+          <t>116134</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -8917,32 +8917,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>150776</t>
+          <t>165714</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>55799</t>
+          <t>143412</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>249802</t>
+          <t>189049</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8952,32 +8952,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>113470</t>
+          <t>123782</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>98007</t>
+          <t>108756</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>128145</t>
+          <t>140318</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8987,32 +8987,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>264247</t>
+          <t>289496</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>121253</t>
+          <t>260072</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>357903</t>
+          <t>317108</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>36,27%</t>
         </is>
       </c>
     </row>
@@ -9030,32 +9030,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>102200</t>
+          <t>116652</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40799</t>
+          <t>95022</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>169223</t>
+          <t>139886</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9065,32 +9065,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>86213</t>
+          <t>98325</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72169</t>
+          <t>82594</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>100388</t>
+          <t>113990</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9100,32 +9100,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>188413</t>
+          <t>214977</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>84246</t>
+          <t>185884</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>253221</t>
+          <t>242370</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -9143,32 +9143,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>51403</t>
+          <t>63649</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20064</t>
+          <t>46720</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>89015</t>
+          <t>87465</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9178,32 +9178,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>60572</t>
+          <t>67549</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>47664</t>
+          <t>53855</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>73791</t>
+          <t>82070</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9213,32 +9213,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>111975</t>
+          <t>131199</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>51063</t>
+          <t>108077</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>154954</t>
+          <t>156469</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -9256,17 +9256,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>669961</t>
+          <t>478773</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>669961</t>
+          <t>478773</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>669961</t>
+          <t>478773</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9291,17 +9291,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>355005</t>
+          <t>395428</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>355005</t>
+          <t>395428</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>355005</t>
+          <t>395428</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9326,17 +9326,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1024967</t>
+          <t>874201</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1024967</t>
+          <t>874201</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1024967</t>
+          <t>874201</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
